--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2677B50E-7DEA-4B6D-B7C5-6FCA610385F0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541BD34E-04D7-4097-9DB6-DA1B5BC1AF58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -416,6 +416,13 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -423,13 +430,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -956,7 +956,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="39" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -1021,11 +1021,19 @@
       <c r="B11" s="29">
         <v>46114</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="34"/>
+      <c r="C11" s="35">
+        <v>326938</v>
+      </c>
+      <c r="D11" s="35">
+        <v>308187.25</v>
+      </c>
+      <c r="E11" s="34">
+        <v>197.25</v>
+      </c>
       <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="G11" s="35">
+        <v>1944</v>
+      </c>
       <c r="H11" s="34"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1046,14 +1054,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1073,14 +1081,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1100,14 +1108,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1277,14 +1285,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1454,14 +1462,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -1482,7 +1490,7 @@
         <v>46132</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="43"/>
+      <c r="D29" s="40"/>
       <c r="E29" s="15"/>
       <c r="F29" s="12"/>
       <c r="G29" s="36"/>
@@ -1507,7 +1515,7 @@
         <v>46133</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="43"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="15"/>
       <c r="F30" s="12"/>
       <c r="G30" s="36"/>
@@ -1532,7 +1540,7 @@
         <v>46134</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="43"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="15"/>
       <c r="F31" s="12"/>
       <c r="G31" s="36"/>
@@ -1557,7 +1565,7 @@
         <v>46135</v>
       </c>
       <c r="C32" s="12"/>
-      <c r="D32" s="43"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="15"/>
       <c r="F32" s="12"/>
       <c r="G32" s="36"/>
@@ -1582,7 +1590,7 @@
         <v>46136</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="43"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="15"/>
       <c r="F33" s="12"/>
       <c r="G33" s="36"/>
@@ -1607,7 +1615,7 @@
         <v>46137</v>
       </c>
       <c r="C34" s="12"/>
-      <c r="D34" s="43"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="15"/>
       <c r="F34" s="12"/>
       <c r="G34" s="36"/>
@@ -1631,14 +1639,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="41"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -1684,7 +1692,7 @@
         <v>46140</v>
       </c>
       <c r="C37" s="26"/>
-      <c r="D37" s="44"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="15"/>
       <c r="F37" s="12"/>
       <c r="G37" s="36"/>
@@ -1709,7 +1717,7 @@
         <v>46141</v>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="44"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="15"/>
       <c r="F38" s="12"/>
       <c r="G38" s="36"/>
@@ -1734,7 +1742,7 @@
         <v>46142</v>
       </c>
       <c r="C39" s="26"/>
-      <c r="D39" s="44"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="15"/>
       <c r="F39" s="12"/>
       <c r="G39" s="36"/>
@@ -1757,7 +1765,7 @@
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="43"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -1827,12 +1835,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>554839</v>
+        <v>881777</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>49.75</v>
+        <v>247</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1840,7 +1848,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5502,7 +5510,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="39" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -5569,11 +5577,19 @@
       <c r="B11" s="29">
         <v>46114</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="34"/>
+      <c r="C11" s="35">
+        <v>278180</v>
+      </c>
+      <c r="D11" s="35">
+        <v>234894.5</v>
+      </c>
+      <c r="E11" s="34">
+        <v>1086.5</v>
+      </c>
       <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="G11" s="35">
+        <v>1944</v>
+      </c>
       <c r="H11" s="34"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -5594,14 +5610,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5621,14 +5637,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -5648,14 +5664,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -5825,14 +5841,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -6002,14 +6018,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -6030,7 +6046,7 @@
         <v>46132</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="43"/>
+      <c r="D29" s="40"/>
       <c r="E29" s="15"/>
       <c r="F29" s="12"/>
       <c r="G29" s="36"/>
@@ -6055,7 +6071,7 @@
         <v>46133</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="43"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="15"/>
       <c r="F30" s="12"/>
       <c r="G30" s="36"/>
@@ -6080,7 +6096,7 @@
         <v>46134</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="43"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="15"/>
       <c r="F31" s="12"/>
       <c r="G31" s="36"/>
@@ -6105,7 +6121,7 @@
         <v>46135</v>
       </c>
       <c r="C32" s="12"/>
-      <c r="D32" s="43"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="15"/>
       <c r="F32" s="12"/>
       <c r="G32" s="36"/>
@@ -6130,7 +6146,7 @@
         <v>46136</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="43"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="15"/>
       <c r="F33" s="12"/>
       <c r="G33" s="36"/>
@@ -6155,7 +6171,7 @@
         <v>46137</v>
       </c>
       <c r="C34" s="12"/>
-      <c r="D34" s="43"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="15"/>
       <c r="F34" s="12"/>
       <c r="G34" s="36"/>
@@ -6179,14 +6195,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="41"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -6232,7 +6248,7 @@
         <v>46140</v>
       </c>
       <c r="C37" s="26"/>
-      <c r="D37" s="44"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="15"/>
       <c r="F37" s="12"/>
       <c r="G37" s="36"/>
@@ -6257,7 +6273,7 @@
         <v>46141</v>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="44"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="15"/>
       <c r="F38" s="12"/>
       <c r="G38" s="36"/>
@@ -6282,7 +6298,7 @@
         <v>46142</v>
       </c>
       <c r="C39" s="26"/>
-      <c r="D39" s="44"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="15"/>
       <c r="F39" s="12"/>
       <c r="G39" s="36"/>
@@ -6305,7 +6321,7 @@
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="43"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -6375,12 +6391,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>356469</v>
+        <v>634649</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>0</v>
+        <v>1086.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6388,7 +6404,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>1356</v>
+        <v>3300</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10050,7 +10066,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="39" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -10117,11 +10133,19 @@
       <c r="B11" s="29">
         <v>46114</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="34"/>
+      <c r="C11" s="35">
+        <v>589177</v>
+      </c>
+      <c r="D11" s="35">
+        <v>497992.75</v>
+      </c>
+      <c r="E11" s="34">
+        <v>144.75</v>
+      </c>
       <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="G11" s="35">
+        <v>3864</v>
+      </c>
       <c r="H11" s="34"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -10142,14 +10166,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10169,14 +10193,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -10196,14 +10220,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -10373,14 +10397,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -10550,14 +10574,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -10578,7 +10602,7 @@
         <v>46132</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="43"/>
+      <c r="D29" s="40"/>
       <c r="E29" s="15"/>
       <c r="F29" s="12"/>
       <c r="G29" s="36"/>
@@ -10603,7 +10627,7 @@
         <v>46133</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="43"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="15"/>
       <c r="F30" s="12"/>
       <c r="G30" s="36"/>
@@ -10628,7 +10652,7 @@
         <v>46134</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="43"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="15"/>
       <c r="F31" s="12"/>
       <c r="G31" s="36"/>
@@ -10653,7 +10677,7 @@
         <v>46135</v>
       </c>
       <c r="C32" s="12"/>
-      <c r="D32" s="43"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="15"/>
       <c r="F32" s="12"/>
       <c r="G32" s="36"/>
@@ -10678,7 +10702,7 @@
         <v>46136</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="43"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="15"/>
       <c r="F33" s="12"/>
       <c r="G33" s="36"/>
@@ -10703,7 +10727,7 @@
         <v>46137</v>
       </c>
       <c r="C34" s="12"/>
-      <c r="D34" s="43"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="15"/>
       <c r="F34" s="12"/>
       <c r="G34" s="36"/>
@@ -10727,14 +10751,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="41"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -10780,7 +10804,7 @@
         <v>46140</v>
       </c>
       <c r="C37" s="26"/>
-      <c r="D37" s="44"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="15"/>
       <c r="F37" s="12"/>
       <c r="G37" s="36"/>
@@ -10805,7 +10829,7 @@
         <v>46141</v>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="44"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="15"/>
       <c r="F38" s="12"/>
       <c r="G38" s="36"/>
@@ -10830,7 +10854,7 @@
         <v>46142</v>
       </c>
       <c r="C39" s="26"/>
-      <c r="D39" s="44"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="15"/>
       <c r="F39" s="12"/>
       <c r="G39" s="36"/>
@@ -10853,7 +10877,7 @@
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="43"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -10923,12 +10947,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>419925</v>
+        <v>1009102</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>211.75</v>
+        <v>356.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10936,7 +10960,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>2226</v>
+        <v>6090</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541BD34E-04D7-4097-9DB6-DA1B5BC1AF58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0254FD-E49A-4EB7-8FFE-85583E148AF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1135,11 +1135,19 @@
       <c r="B15" s="29">
         <v>46118</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="34"/>
+      <c r="C15" s="35">
+        <v>941474</v>
+      </c>
+      <c r="D15" s="35">
+        <v>796366.25</v>
+      </c>
+      <c r="E15" s="34">
+        <v>864.25</v>
+      </c>
       <c r="F15" s="34"/>
-      <c r="G15" s="37"/>
+      <c r="G15" s="37">
+        <v>6552</v>
+      </c>
       <c r="H15" s="34"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1835,12 +1843,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>881777</v>
+        <v>1823251</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>247</v>
+        <v>1111.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1848,7 +1856,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>1944</v>
+        <v>8496</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5691,11 +5699,19 @@
       <c r="B15" s="29">
         <v>46118</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
+      <c r="C15" s="35">
+        <v>488743</v>
+      </c>
+      <c r="D15" s="35">
+        <v>413351.5</v>
+      </c>
       <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="37"/>
+      <c r="F15" s="37">
+        <v>2101.5</v>
+      </c>
+      <c r="G15" s="37">
+        <v>3006</v>
+      </c>
       <c r="H15" s="34"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -6391,7 +6407,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>634649</v>
+        <v>1123392</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6400,11 +6416,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>260</v>
+        <v>2361.5</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>3300</v>
+        <v>6306</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10247,12 +10263,22 @@
       <c r="B15" s="29">
         <v>46118</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="34"/>
+      <c r="C15" s="35">
+        <v>513840</v>
+      </c>
+      <c r="D15" s="35">
+        <v>432927.25</v>
+      </c>
+      <c r="E15" s="34">
+        <v>490.75</v>
+      </c>
       <c r="F15" s="34"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="34"/>
+      <c r="G15" s="37">
+        <v>1866</v>
+      </c>
+      <c r="H15" s="37">
+        <v>50</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -10947,12 +10973,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1009102</v>
+        <v>1522942</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>356.5</v>
+        <v>847.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10960,11 +10986,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>6090</v>
+        <v>7956</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0254FD-E49A-4EB7-8FFE-85583E148AF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9A68FB-497A-4041-9B5A-6110071AA52C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1168,11 +1168,19 @@
       <c r="B16" s="29">
         <v>46119</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="34"/>
+      <c r="C16" s="35">
+        <v>532497</v>
+      </c>
+      <c r="D16" s="35">
+        <v>476691</v>
+      </c>
+      <c r="E16" s="34">
+        <v>2</v>
+      </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="37"/>
+      <c r="G16" s="37">
+        <v>3420</v>
+      </c>
       <c r="H16" s="34"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1843,12 +1851,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1823251</v>
+        <v>2355748</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1111.25</v>
+        <v>1113.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1856,7 +1864,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>8496</v>
+        <v>11916</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5732,11 +5740,19 @@
       <c r="B16" s="29">
         <v>46119</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="34"/>
+      <c r="C16" s="35">
+        <v>321418</v>
+      </c>
+      <c r="D16" s="35">
+        <v>274279</v>
+      </c>
+      <c r="E16" s="34">
+        <v>321</v>
+      </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="37"/>
+      <c r="G16" s="37">
+        <v>1200</v>
+      </c>
       <c r="H16" s="34"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -6407,12 +6423,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1123392</v>
+        <v>1444810</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1086.5</v>
+        <v>1407.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6420,7 +6436,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>6306</v>
+        <v>7506</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10298,11 +10314,19 @@
       <c r="B16" s="29">
         <v>46119</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
+      <c r="C16" s="35">
+        <v>709846</v>
+      </c>
+      <c r="D16" s="35">
+        <v>599689</v>
+      </c>
       <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="37"/>
+      <c r="F16" s="35">
+        <v>320</v>
+      </c>
+      <c r="G16" s="37">
+        <v>4944</v>
+      </c>
       <c r="H16" s="34"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -10973,7 +10997,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1522942</v>
+        <v>2232788</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -10982,11 +11006,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>7956</v>
+        <v>12900</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9A68FB-497A-4041-9B5A-6110071AA52C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47A4F28-F43F-4F00-A566-3AB07FDF060A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1201,11 +1201,19 @@
       <c r="B17" s="29">
         <v>46120</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="35">
+        <v>415545</v>
+      </c>
+      <c r="D17" s="35">
+        <v>355503.75</v>
+      </c>
+      <c r="E17" s="34">
+        <v>1003.75</v>
+      </c>
       <c r="F17" s="34"/>
-      <c r="G17" s="37"/>
+      <c r="G17" s="37">
+        <v>2592</v>
+      </c>
       <c r="H17" s="34"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1851,12 +1859,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2355748</v>
+        <v>2771293</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1113.25</v>
+        <v>2117</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1864,7 +1872,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>11916</v>
+        <v>14508</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5773,11 +5781,19 @@
       <c r="B17" s="29">
         <v>46120</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="35">
+        <v>286224</v>
+      </c>
+      <c r="D17" s="35">
+        <v>238710.75</v>
+      </c>
+      <c r="E17" s="34">
+        <v>667.75</v>
+      </c>
       <c r="F17" s="34"/>
-      <c r="G17" s="37"/>
+      <c r="G17" s="37">
+        <v>1494</v>
+      </c>
       <c r="H17" s="34"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -6423,12 +6439,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1444810</v>
+        <v>1731034</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1407.5</v>
+        <v>2075.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6436,7 +6452,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>7506</v>
+        <v>9000</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10347,12 +10363,22 @@
       <c r="B17" s="29">
         <v>46120</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="35">
+        <v>546916</v>
+      </c>
+      <c r="D17" s="35">
+        <v>461549</v>
+      </c>
+      <c r="E17" s="34">
+        <v>854</v>
+      </c>
       <c r="F17" s="34"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="37">
+        <v>4044</v>
+      </c>
+      <c r="H17" s="35">
+        <v>50</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -10997,12 +11023,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2232788</v>
+        <v>2779704</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>847.25</v>
+        <v>1701.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11010,11 +11036,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>12900</v>
+        <v>16944</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47A4F28-F43F-4F00-A566-3AB07FDF060A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DC210D-F2A2-46AC-87E4-FC5F376AF860}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -5785,10 +5785,10 @@
         <v>286224</v>
       </c>
       <c r="D17" s="35">
-        <v>238710.75</v>
+        <v>286224</v>
       </c>
       <c r="E17" s="34">
-        <v>667.75</v>
+        <v>583.75</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="37">
@@ -6444,7 +6444,7 @@
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2075.25</v>
+        <v>1991.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DC210D-F2A2-46AC-87E4-FC5F376AF860}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B308E86C-EAC3-428D-ACDB-691B82E2153E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1234,10 +1234,16 @@
       <c r="B18" s="29">
         <v>46121</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35">
+        <v>426678</v>
+      </c>
+      <c r="D18" s="35">
+        <v>366426</v>
+      </c>
       <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
+      <c r="F18" s="35">
+        <v>1251</v>
+      </c>
       <c r="G18" s="37"/>
       <c r="H18" s="34"/>
       <c r="I18" s="1"/>
@@ -1859,7 +1865,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2771293</v>
+        <v>3197971</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1868,7 +1874,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>0</v>
+        <v>1251</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5814,11 +5820,19 @@
       <c r="B18" s="29">
         <v>46121</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="34"/>
+      <c r="C18" s="35">
+        <v>256965</v>
+      </c>
+      <c r="D18" s="35">
+        <v>217815</v>
+      </c>
+      <c r="E18" s="34">
+        <v>187</v>
+      </c>
       <c r="F18" s="34"/>
-      <c r="G18" s="37"/>
+      <c r="G18" s="37">
+        <v>1296</v>
+      </c>
       <c r="H18" s="34"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -6439,12 +6453,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1731034</v>
+        <v>1987999</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1991.25</v>
+        <v>2178.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6452,7 +6466,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>9000</v>
+        <v>10296</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10398,11 +10412,19 @@
       <c r="B18" s="29">
         <v>46121</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35">
+        <v>448958</v>
+      </c>
+      <c r="D18" s="35">
+        <v>366583.25</v>
+      </c>
       <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="37"/>
+      <c r="F18" s="35">
+        <v>1663.75</v>
+      </c>
+      <c r="G18" s="37">
+        <v>1296</v>
+      </c>
       <c r="H18" s="34"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -11023,7 +11045,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2779704</v>
+        <v>3228662</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11032,11 +11054,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>320</v>
+        <v>1983.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>16944</v>
+        <v>18240</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B308E86C-EAC3-428D-ACDB-691B82E2153E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01748F50-5C2C-460C-9988-4AB50071F278}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="20">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>HOLIDAY - HOLY WEEK</t>
+  </si>
+  <si>
+    <t>NO TRIP</t>
   </si>
 </sst>
 </file>
@@ -1265,10 +1268,16 @@
       <c r="B19" s="29">
         <v>46122</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
+      <c r="C19" s="35">
+        <v>291054.08000000002</v>
+      </c>
+      <c r="D19" s="35">
+        <v>245777.33</v>
+      </c>
       <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="F19" s="35">
+        <v>104.67</v>
+      </c>
       <c r="G19" s="37"/>
       <c r="H19" s="34"/>
       <c r="I19" s="1"/>
@@ -1865,7 +1874,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3197971</v>
+        <v>3489025.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>1251</v>
+        <v>1355.67</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5853,11 +5862,19 @@
       <c r="B19" s="29">
         <v>46122</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
+      <c r="C19" s="35">
+        <v>337013</v>
+      </c>
+      <c r="D19" s="35">
+        <v>300227.75</v>
+      </c>
       <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="37"/>
+      <c r="F19" s="35">
+        <v>112.25</v>
+      </c>
+      <c r="G19" s="37">
+        <v>1200</v>
+      </c>
       <c r="H19" s="34"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -6453,7 +6470,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>1987999</v>
+        <v>2325012</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6462,11 +6479,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2361.5</v>
+        <v>2473.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>10296</v>
+        <v>11496</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10445,12 +10462,14 @@
       <c r="B19" s="29">
         <v>46122</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="34"/>
+      <c r="C19" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -14521,13 +14540,14 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01748F50-5C2C-460C-9988-4AB50071F278}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66952EC0-6AE4-4D6E-9743-0E8CB1F95EEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>NO TRIP</t>
+  </si>
+  <si>
+    <t>DAY OFF</t>
   </si>
 </sst>
 </file>
@@ -1299,12 +1302,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="34"/>
+      <c r="C20" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1351,12 +1356,23 @@
       <c r="B22" s="29">
         <v>46125</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="35">
+        <v>240718</v>
+      </c>
+      <c r="D22" s="35">
+        <v>188040.89</v>
+      </c>
+      <c r="E22" s="34">
+        <v>110.39</v>
+      </c>
       <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
+      <c r="G22" s="37">
+        <f>1296</f>
+        <v>1296</v>
+      </c>
+      <c r="H22" s="37">
+        <v>174.11</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1874,12 +1890,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3489025.08</v>
+        <v>3729743.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2117</v>
+        <v>2227.39</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1887,11 +1903,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>14508</v>
+        <v>15804</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>0</v>
+        <v>174.11</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5350,13 +5366,14 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -5895,12 +5912,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="34"/>
+      <c r="C20" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -5947,11 +5966,19 @@
       <c r="B22" s="29">
         <v>46125</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="35">
+        <v>304172</v>
+      </c>
+      <c r="D22" s="35">
+        <v>257400.5</v>
+      </c>
+      <c r="E22" s="34">
+        <v>1453.5</v>
+      </c>
       <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
+      <c r="G22" s="37">
+        <v>1944</v>
+      </c>
       <c r="H22" s="37"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -6470,12 +6497,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2325012</v>
+        <v>2629184</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2178.25</v>
+        <v>3631.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6483,7 +6510,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>11496</v>
+        <v>13440</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -9946,13 +9973,14 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10489,12 +10517,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="34"/>
+      <c r="C20" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -10541,12 +10571,22 @@
       <c r="B22" s="29">
         <v>46125</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="35">
+        <v>328634</v>
+      </c>
+      <c r="D22" s="35">
+        <v>278277.75</v>
+      </c>
+      <c r="E22" s="34">
+        <v>427.75</v>
+      </c>
       <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
+      <c r="G22" s="37">
+        <v>1920</v>
+      </c>
+      <c r="H22" s="37">
+        <v>50</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -11064,12 +11104,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3228662</v>
+        <v>3557296</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>1701.25</v>
+        <v>2129</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11077,11 +11117,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>18240</v>
+        <v>20160</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14540,7 +14580,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -14548,6 +14588,7 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66952EC0-6AE4-4D6E-9743-0E8CB1F95EEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D939B6BD-14C5-4704-A8C2-0A6F26344BBD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1392,11 +1392,19 @@
       <c r="B23" s="29">
         <v>46126</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
+      <c r="C23" s="35">
+        <v>270579</v>
+      </c>
+      <c r="D23" s="35">
+        <v>231296.25</v>
+      </c>
       <c r="E23" s="34"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
+      <c r="F23" s="37">
+        <v>678.75</v>
+      </c>
+      <c r="G23" s="37">
+        <v>60</v>
+      </c>
       <c r="H23" s="37"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1890,7 +1898,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3729743.08</v>
+        <v>4000322.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1899,11 +1907,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>1355.67</v>
+        <v>2034.42</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>15804</v>
+        <v>15864</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5999,11 +6007,19 @@
       <c r="B23" s="29">
         <v>46126</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="34"/>
+      <c r="C23" s="35">
+        <v>326754</v>
+      </c>
+      <c r="D23" s="35">
+        <v>273274.5</v>
+      </c>
+      <c r="E23" s="34">
+        <v>206.5</v>
+      </c>
       <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
+      <c r="G23" s="37">
+        <v>2286</v>
+      </c>
       <c r="H23" s="37"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -6497,12 +6513,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2629184</v>
+        <v>2955938</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>3631.75</v>
+        <v>3838.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6510,7 +6526,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>13440</v>
+        <v>15726</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10606,11 +10622,19 @@
       <c r="B23" s="29">
         <v>46126</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
+      <c r="C23" s="35">
+        <v>447818</v>
+      </c>
+      <c r="D23" s="35">
+        <v>384131</v>
+      </c>
       <c r="E23" s="34"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
+      <c r="F23" s="37">
+        <v>561</v>
+      </c>
+      <c r="G23" s="37">
+        <v>2856</v>
+      </c>
       <c r="H23" s="37"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -11104,7 +11128,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3557296</v>
+        <v>4005114</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11113,11 +11137,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>1983.75</v>
+        <v>2544.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>20160</v>
+        <v>23016</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D939B6BD-14C5-4704-A8C2-0A6F26344BBD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D2F7F3-EA1A-4D38-ADA7-274FD4628BE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1425,11 +1425,19 @@
       <c r="B24" s="29">
         <v>46127</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="35">
+        <v>376385</v>
+      </c>
+      <c r="D24" s="35">
+        <v>274893</v>
+      </c>
+      <c r="E24" s="34">
+        <v>1406</v>
+      </c>
       <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
+      <c r="G24" s="37">
+        <v>1476</v>
+      </c>
       <c r="H24" s="37"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1898,12 +1906,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4000322.08</v>
+        <v>4376707.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2227.39</v>
+        <v>3633.39</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1911,7 +1919,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>15864</v>
+        <v>17340</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -6040,11 +6048,19 @@
       <c r="B24" s="29">
         <v>46127</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
+      <c r="C24" s="35">
+        <v>295167</v>
+      </c>
+      <c r="D24" s="35">
+        <v>245640</v>
+      </c>
       <c r="E24" s="34"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
+      <c r="F24" s="37">
+        <v>329</v>
+      </c>
+      <c r="G24" s="37">
+        <v>2010</v>
+      </c>
       <c r="H24" s="37"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -6513,7 +6529,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2955938</v>
+        <v>3251105</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6522,11 +6538,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2473.75</v>
+        <v>2802.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>15726</v>
+        <v>17736</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10655,12 +10671,23 @@
       <c r="B24" s="29">
         <v>46127</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="35">
+        <v>547376</v>
+      </c>
+      <c r="D24" s="35">
+        <v>477853</v>
+      </c>
+      <c r="E24" s="34">
+        <v>300.5</v>
+      </c>
       <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
+      <c r="G24" s="37">
+        <f>2064</f>
+        <v>2064</v>
+      </c>
+      <c r="H24" s="37">
+        <v>50</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -11128,12 +11155,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4005114</v>
+        <v>4552490</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2129</v>
+        <v>2429.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11141,11 +11168,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>23016</v>
+        <v>25080</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D2F7F3-EA1A-4D38-ADA7-274FD4628BE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90514969-F59A-4D63-93BF-0E24C43ACB3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1458,12 +1458,20 @@
       <c r="B25" s="29">
         <v>46128</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
+      <c r="C25" s="35">
+        <v>288771</v>
+      </c>
+      <c r="D25" s="35">
+        <v>314444.5</v>
+      </c>
       <c r="E25" s="34"/>
-      <c r="F25" s="37"/>
+      <c r="F25" s="37">
+        <v>828.5</v>
+      </c>
       <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
+      <c r="H25" s="37">
+        <v>40</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -1906,7 +1914,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4376707.08</v>
+        <v>4665478.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1915,7 +1923,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2034.42</v>
+        <v>2862.92</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -1923,7 +1931,7 @@
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>174.11</v>
+        <v>214.11</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -6081,11 +6089,19 @@
       <c r="B25" s="29">
         <v>46128</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
+      <c r="C25" s="35">
+        <v>292871</v>
+      </c>
+      <c r="D25" s="35">
+        <v>246705.5</v>
+      </c>
       <c r="E25" s="34"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="F25" s="37">
+        <v>524.5</v>
+      </c>
+      <c r="G25" s="37">
+        <v>1536</v>
+      </c>
       <c r="H25" s="37"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -6529,7 +6545,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3251105</v>
+        <v>3543976</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6538,11 +6554,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2802.75</v>
+        <v>3327.25</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>17736</v>
+        <v>19272</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10707,11 +10723,19 @@
       <c r="B25" s="29">
         <v>46128</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
+      <c r="C25" s="35">
+        <v>402605</v>
+      </c>
+      <c r="D25" s="35">
+        <v>339884</v>
+      </c>
       <c r="E25" s="34"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="F25" s="37">
+        <v>380</v>
+      </c>
+      <c r="G25" s="37">
+        <v>2496</v>
+      </c>
       <c r="H25" s="37"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -11155,7 +11179,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4552490</v>
+        <v>4955095</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11164,11 +11188,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2544.75</v>
+        <v>2924.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>25080</v>
+        <v>27576</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90514969-F59A-4D63-93BF-0E24C43ACB3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E373AE-B2CC-4B37-8BAD-76BD44956185}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1491,12 +1491,14 @@
       <c r="B26" s="29">
         <v>46129</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
+      <c r="C26" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="19"/>
@@ -5390,7 +5392,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -5398,6 +5400,7 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C26:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6122,11 +6125,19 @@
       <c r="B26" s="29">
         <v>46129</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="34"/>
+      <c r="C26" s="35">
+        <v>274543</v>
+      </c>
+      <c r="D26" s="35">
+        <v>235897</v>
+      </c>
+      <c r="E26" s="34">
+        <v>38</v>
+      </c>
       <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
+      <c r="G26" s="37">
+        <v>1200</v>
+      </c>
       <c r="H26" s="37"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -6545,12 +6556,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3543976</v>
+        <v>3818519</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>3838.25</v>
+        <v>3876.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6558,7 +6569,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>19272</v>
+        <v>20472</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10756,11 +10767,19 @@
       <c r="B26" s="29">
         <v>46129</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
+      <c r="C26" s="35">
+        <v>442271</v>
+      </c>
+      <c r="D26" s="35">
+        <v>375419</v>
+      </c>
       <c r="E26" s="34"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
+      <c r="F26" s="37">
+        <v>11107</v>
+      </c>
+      <c r="G26" s="37">
+        <v>2928</v>
+      </c>
       <c r="H26" s="37"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -11179,7 +11198,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4955095</v>
+        <v>5397366</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11188,11 +11207,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2924.75</v>
+        <v>14031.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>27576</v>
+        <v>30504</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E373AE-B2CC-4B37-8BAD-76BD44956185}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ECB772-2169-4580-88D0-12215F270277}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1518,12 +1518,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
+      <c r="C27" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1570,11 +1572,19 @@
       <c r="B29" s="29">
         <v>46132</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="15"/>
+      <c r="C29" s="12">
+        <v>547809</v>
+      </c>
+      <c r="D29" s="40">
+        <v>443992.5</v>
+      </c>
+      <c r="E29" s="15">
+        <v>162.5</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="36"/>
+      <c r="G29" s="36">
+        <v>3312</v>
+      </c>
       <c r="H29" s="32"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1916,12 +1926,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4665478.08</v>
+        <v>5213287.08</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>3633.39</v>
+        <v>3795.89</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -1929,7 +1939,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>17340</v>
+        <v>20652</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -5392,7 +5402,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -5401,6 +5411,7 @@
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6158,12 +6169,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
+      <c r="C27" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -6210,10 +6223,16 @@
       <c r="B29" s="29">
         <v>46132</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="40"/>
+      <c r="C29" s="12">
+        <v>387918</v>
+      </c>
+      <c r="D29" s="40">
+        <v>329710.5</v>
+      </c>
       <c r="E29" s="15"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="12">
+        <v>54.5</v>
+      </c>
       <c r="G29" s="36"/>
       <c r="H29" s="32"/>
       <c r="I29" s="1"/>
@@ -6556,7 +6575,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3818519</v>
+        <v>4206437</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6565,7 +6584,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3327.25</v>
+        <v>3381.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -10032,7 +10051,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -10040,6 +10059,7 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10800,12 +10820,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
+      <c r="C27" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -10852,12 +10874,22 @@
       <c r="B29" s="29">
         <v>46132</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="15"/>
+      <c r="C29" s="12">
+        <v>394839</v>
+      </c>
+      <c r="D29" s="40">
+        <v>394839</v>
+      </c>
+      <c r="E29" s="15">
+        <v>10236.5</v>
+      </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="32"/>
+      <c r="G29" s="36">
+        <v>1956</v>
+      </c>
+      <c r="H29" s="32">
+        <v>50</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -11198,12 +11230,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5397366</v>
+        <v>5792205</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>2429.5</v>
+        <v>12666</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11211,11 +11243,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>30504</v>
+        <v>32460</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14674,7 +14706,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -14683,6 +14715,7 @@
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ECB772-2169-4580-88D0-12215F270277}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC7AA82-2839-40B3-AC7A-F5BB5B894551}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1605,11 +1605,19 @@
       <c r="B30" s="29">
         <v>46133</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="40"/>
+      <c r="C30" s="12">
+        <v>439067</v>
+      </c>
+      <c r="D30" s="40">
+        <v>380276.75</v>
+      </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="36"/>
+      <c r="F30" s="12">
+        <v>580.25</v>
+      </c>
+      <c r="G30" s="36">
+        <v>2622</v>
+      </c>
       <c r="H30" s="32"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1926,7 +1934,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5213287.08</v>
+        <v>5652354.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1935,11 +1943,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>2862.92</v>
+        <v>3443.17</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>20652</v>
+        <v>23274</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -6254,11 +6262,19 @@
       <c r="B30" s="29">
         <v>46133</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="40"/>
+      <c r="C30" s="12">
+        <v>302792</v>
+      </c>
+      <c r="D30" s="40">
+        <v>254528</v>
+      </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="36"/>
+      <c r="F30" s="12">
+        <v>613</v>
+      </c>
+      <c r="G30" s="36">
+        <v>1332</v>
+      </c>
       <c r="H30" s="32"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -6575,7 +6591,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4206437</v>
+        <v>4509229</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6584,11 +6600,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3381.75</v>
+        <v>3994.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>20472</v>
+        <v>21804</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10909,11 +10925,19 @@
       <c r="B30" s="29">
         <v>46133</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="15"/>
+      <c r="C30" s="12">
+        <v>454803</v>
+      </c>
+      <c r="D30" s="40">
+        <v>390153.75</v>
+      </c>
+      <c r="E30" s="15">
+        <v>15223.75</v>
+      </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="36"/>
+      <c r="G30" s="36">
+        <v>3156</v>
+      </c>
       <c r="H30" s="32"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -11230,12 +11254,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5792205</v>
+        <v>6247008</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>12666</v>
+        <v>27889.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11243,7 +11267,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>32460</v>
+        <v>35616</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC7AA82-2839-40B3-AC7A-F5BB5B894551}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D86E4C-98B5-4F45-A417-36692DB69E10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1638,9 +1638,15 @@
       <c r="B31" s="29">
         <v>46134</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="15"/>
+      <c r="C31" s="12">
+        <v>240726</v>
+      </c>
+      <c r="D31" s="40">
+        <v>206967</v>
+      </c>
+      <c r="E31" s="15">
+        <v>434</v>
+      </c>
       <c r="F31" s="12"/>
       <c r="G31" s="36"/>
       <c r="H31" s="32"/>
@@ -1934,12 +1940,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5652354.0800000001</v>
+        <v>5893080.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>3795.89</v>
+        <v>4229.8899999999994</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6295,11 +6301,19 @@
       <c r="B31" s="29">
         <v>46134</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="15"/>
+      <c r="C31" s="12">
+        <v>262492</v>
+      </c>
+      <c r="D31" s="40">
+        <v>222119.5</v>
+      </c>
+      <c r="E31" s="15">
+        <v>152.5</v>
+      </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="36"/>
+      <c r="G31" s="36">
+        <v>1944</v>
+      </c>
       <c r="H31" s="32"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -6591,12 +6605,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4509229</v>
+        <v>4771721</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>3876.25</v>
+        <v>4028.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6604,7 +6618,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>21804</v>
+        <v>23748</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10958,12 +10972,22 @@
       <c r="B31" s="29">
         <v>46134</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="15"/>
+      <c r="C31" s="12">
+        <v>359940</v>
+      </c>
+      <c r="D31" s="40">
+        <v>306970</v>
+      </c>
+      <c r="E31" s="15">
+        <v>806</v>
+      </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="32"/>
+      <c r="G31" s="36">
+        <v>1758</v>
+      </c>
+      <c r="H31" s="32">
+        <v>50</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="19"/>
@@ -11254,12 +11278,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6247008</v>
+        <v>6606948</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>27889.75</v>
+        <v>28695.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11267,11 +11291,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>35616</v>
+        <v>37374</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D86E4C-98B5-4F45-A417-36692DB69E10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BE3597-9922-442D-B4A0-F361DC44067D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1669,9 +1669,15 @@
       <c r="B32" s="29">
         <v>46135</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="15"/>
+      <c r="C32" s="12">
+        <v>366981</v>
+      </c>
+      <c r="D32" s="40">
+        <v>250535.25</v>
+      </c>
+      <c r="E32" s="15">
+        <v>394.25</v>
+      </c>
       <c r="F32" s="12"/>
       <c r="G32" s="36"/>
       <c r="H32" s="32"/>
@@ -1940,12 +1946,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5893080.0800000001</v>
+        <v>6260061.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>4229.8899999999994</v>
+        <v>4624.1399999999994</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6334,11 +6340,19 @@
       <c r="B32" s="29">
         <v>46135</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="40"/>
+      <c r="C32" s="12">
+        <v>289540</v>
+      </c>
+      <c r="D32" s="40">
+        <v>238440.25</v>
+      </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="36"/>
+      <c r="F32" s="12">
+        <v>136.75</v>
+      </c>
+      <c r="G32" s="36">
+        <v>2130</v>
+      </c>
       <c r="H32" s="32"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -6605,7 +6619,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4771721</v>
+        <v>5061261</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6614,11 +6628,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3994.75</v>
+        <v>4131.5</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>23748</v>
+        <v>25878</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -11007,12 +11021,22 @@
       <c r="B32" s="29">
         <v>46135</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="40"/>
+      <c r="C32" s="12">
+        <v>315337</v>
+      </c>
+      <c r="D32" s="40">
+        <v>254584</v>
+      </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="32"/>
+      <c r="F32" s="12">
+        <v>1337</v>
+      </c>
+      <c r="G32" s="36">
+        <v>648</v>
+      </c>
+      <c r="H32" s="32">
+        <v>26145</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -11278,7 +11302,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6606948</v>
+        <v>6922285</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11287,15 +11311,15 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>14031.75</v>
+        <v>15368.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>37374</v>
+        <v>38022</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>300</v>
+        <v>26445</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BE3597-9922-442D-B4A0-F361DC44067D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14E62D-665A-47BB-8900-119038865EBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1700,12 +1700,16 @@
       <c r="B33" s="29">
         <v>46136</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="32"/>
+      <c r="C33" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="32">
+        <v>71260</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -1725,12 +1729,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="32"/>
+      <c r="C34" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -1963,7 +1969,7 @@
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>214.11</v>
+        <v>71474.11</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5422,7 +5428,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -5432,6 +5438,8 @@
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6373,11 +6381,19 @@
       <c r="B33" s="29">
         <v>46136</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="15"/>
+      <c r="C33" s="12">
+        <v>233535</v>
+      </c>
+      <c r="D33" s="40">
+        <v>197946.75</v>
+      </c>
+      <c r="E33" s="15">
+        <v>8.75</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="36"/>
+      <c r="G33" s="36">
+        <v>648</v>
+      </c>
       <c r="H33" s="32"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -6398,12 +6414,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="32"/>
+      <c r="C34" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -6619,12 +6637,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5061261</v>
+        <v>5294796</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>4028.75</v>
+        <v>4037.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6632,7 +6650,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>25878</v>
+        <v>26526</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10095,7 +10113,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -10104,6 +10122,7 @@
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11056,12 +11075,22 @@
       <c r="B33" s="29">
         <v>46136</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="15"/>
+      <c r="C33" s="12">
+        <v>299078</v>
+      </c>
+      <c r="D33" s="40">
+        <v>254793</v>
+      </c>
+      <c r="E33" s="15">
+        <v>1617</v>
+      </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="32"/>
+      <c r="G33" s="36">
+        <v>906</v>
+      </c>
+      <c r="H33" s="32">
+        <v>50</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -11081,12 +11110,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="32"/>
+      <c r="C34" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -11302,12 +11333,12 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6922285</v>
+        <v>7221363</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
         <f>SUM(E10:E42)</f>
-        <v>28695.75</v>
+        <v>30312.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -11315,11 +11346,11 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>38022</v>
+        <v>38928</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>26445</v>
+        <v>26495</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -14778,7 +14809,7 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -14788,6 +14819,7 @@
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14E62D-665A-47BB-8900-119038865EBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F50DE7-70C6-45B9-A736-93490CA71D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="21">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -360,7 +360,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -438,6 +438,7 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1783,11 +1784,19 @@
       <c r="B36" s="29">
         <v>46139</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="C36" s="12">
+        <v>533755</v>
+      </c>
+      <c r="D36" s="12">
+        <v>440851.75</v>
+      </c>
       <c r="E36" s="13"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="36"/>
+      <c r="F36" s="12">
+        <v>3133.25</v>
+      </c>
+      <c r="G36" s="36">
+        <v>3888</v>
+      </c>
       <c r="H36" s="33"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -1952,7 +1961,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6260061.0800000001</v>
+        <v>6793816.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1961,11 +1970,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3443.17</v>
+        <v>6576.42</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>23274</v>
+        <v>27162</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -6468,12 +6477,14 @@
       <c r="B36" s="29">
         <v>46139</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="33"/>
+      <c r="C36" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -10113,7 +10124,8 @@
       <c r="F279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="C36:H36"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
@@ -11164,12 +11176,22 @@
       <c r="B36" s="29">
         <v>46139</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="C36" s="12">
+        <v>467478</v>
+      </c>
+      <c r="D36" s="12">
+        <v>395836</v>
+      </c>
       <c r="E36" s="13"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="33"/>
+      <c r="F36" s="12">
+        <v>1591</v>
+      </c>
+      <c r="G36" s="36">
+        <v>3036</v>
+      </c>
+      <c r="H36" s="45">
+        <v>50</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -11333,7 +11355,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7221363</v>
+        <v>7688841</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11342,15 +11364,15 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>15368.75</v>
+        <v>16959.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>38928</v>
+        <v>41964</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>26495</v>
+        <v>26545</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F50DE7-70C6-45B9-A736-93490CA71D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD25F68F-266B-49FE-B16E-2E69110AFC55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -429,6 +429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -438,7 +439,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1061,14 +1061,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1088,14 +1088,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1115,14 +1115,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1303,14 +1303,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1330,14 +1330,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="45"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1492,14 +1492,14 @@
       <c r="B26" s="29">
         <v>46129</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="19"/>
@@ -1519,14 +1519,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1546,14 +1546,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -1701,13 +1701,13 @@
       <c r="B33" s="29">
         <v>46136</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="45"/>
       <c r="H33" s="32">
         <v>71260</v>
       </c>
@@ -1730,14 +1730,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="45"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -1757,14 +1757,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="45"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -1785,14 +1785,14 @@
         <v>46139</v>
       </c>
       <c r="C36" s="12">
-        <v>533755</v>
+        <v>536879</v>
       </c>
       <c r="D36" s="12">
-        <v>440851.75</v>
+        <v>443975.75</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="12">
-        <v>3133.25</v>
+        <v>9.25</v>
       </c>
       <c r="G36" s="36">
         <v>3888</v>
@@ -1961,7 +1961,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6793816.0800000001</v>
+        <v>6796940.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>6576.42</v>
+        <v>3452.42</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -5741,14 +5741,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5768,14 +5768,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -5795,14 +5795,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -5987,14 +5987,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -6014,14 +6014,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="45"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -6206,14 +6206,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -6233,14 +6233,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -6423,14 +6423,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="45"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -6450,14 +6450,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="45"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -6477,14 +6477,14 @@
       <c r="B36" s="29">
         <v>46139</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C36" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="45"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -10125,16 +10125,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C34:H34"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10427,14 +10427,14 @@
       <c r="B12" s="29">
         <v>46115</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10454,14 +10454,14 @@
       <c r="B13" s="29">
         <v>46116</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -10481,14 +10481,14 @@
       <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -10644,14 +10644,14 @@
       <c r="B19" s="29">
         <v>46122</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="45"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -10671,14 +10671,14 @@
       <c r="B20" s="29">
         <v>46123</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -10698,14 +10698,14 @@
       <c r="B21" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="45"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -10895,14 +10895,14 @@
       <c r="B27" s="29">
         <v>46130</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -10922,14 +10922,14 @@
       <c r="B28" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -11122,14 +11122,14 @@
       <c r="B34" s="29">
         <v>46137</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="45"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -11149,14 +11149,14 @@
       <c r="B35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="45"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -11189,7 +11189,7 @@
       <c r="G36" s="36">
         <v>3036</v>
       </c>
-      <c r="H36" s="45">
+      <c r="H36" s="42">
         <v>50</v>
       </c>
       <c r="I36" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD25F68F-266B-49FE-B16E-2E69110AFC55}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B315C0-E2D0-4207-8D19-F471C0F8B4A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1817,12 +1817,22 @@
       <c r="B37" s="29">
         <v>46140</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="41"/>
+      <c r="C37" s="12">
+        <v>386508</v>
+      </c>
+      <c r="D37" s="12">
+        <v>331469.39</v>
+      </c>
       <c r="E37" s="15"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="32"/>
+      <c r="F37" s="12">
+        <v>69.61</v>
+      </c>
+      <c r="G37" s="36">
+        <v>2742</v>
+      </c>
+      <c r="H37" s="32">
+        <v>92.86</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -1961,7 +1971,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6796940.0800000001</v>
+        <v>7183448.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -1970,15 +1980,15 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3452.42</v>
+        <v>3522.03</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>27162</v>
+        <v>29904</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>71474.11</v>
+        <v>71566.97</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -6504,12 +6514,20 @@
       <c r="B37" s="29">
         <v>46140</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="32"/>
+      <c r="C37" s="12">
+        <v>661760</v>
+      </c>
+      <c r="D37" s="12">
+        <v>566092.25</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12">
+        <v>1357.75</v>
+      </c>
+      <c r="G37" s="12">
+        <v>4686</v>
+      </c>
+      <c r="H37" s="12"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -6648,7 +6666,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5294796</v>
+        <v>5956556</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -6657,11 +6675,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>4131.5</v>
+        <v>5489.25</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>26526</v>
+        <v>31212</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -10125,16 +10143,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C35:H35"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C35:H35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11211,12 +11229,20 @@
       <c r="B37" s="29">
         <v>46140</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="32"/>
+      <c r="C37" s="12">
+        <v>487143</v>
+      </c>
+      <c r="D37" s="12">
+        <v>412187.25</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12">
+        <v>154.75</v>
+      </c>
+      <c r="G37" s="36">
+        <v>3480</v>
+      </c>
+      <c r="H37" s="42"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -11355,7 +11381,7 @@
       <c r="B43" s="29"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7688841</v>
+        <v>8175984</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="30">
@@ -11364,11 +11390,11 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>16959.75</v>
+        <v>17114.5</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>41964</v>
+        <v>45444</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B315C0-E2D0-4207-8D19-F471C0F8B4A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE3056-F818-4800-BE1A-C4BE35EBA5C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -360,7 +360,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -401,9 +401,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -426,9 +423,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -963,7 +957,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -994,21 +988,21 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="28">
         <v>46113</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>554839</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <v>477269.75</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>49.75</v>
       </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="34"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1025,23 +1019,23 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="28">
         <v>46114</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>326938</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>308187.25</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="33">
         <v>197.25</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35">
+      <c r="F11" s="33"/>
+      <c r="G11" s="34">
         <v>1944</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1058,17 +1052,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <v>46115</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1085,17 +1079,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="28">
         <v>46116</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1112,17 +1106,17 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1139,23 +1133,23 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="28">
         <v>46118</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <v>941474</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="34">
         <v>796366.25</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="33">
         <v>864.25</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="37">
+      <c r="F15" s="33"/>
+      <c r="G15" s="36">
         <v>6552</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1172,23 +1166,23 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <v>46119</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="34">
         <v>532497</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <v>476691</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="33">
         <v>2</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="37">
+      <c r="F16" s="33"/>
+      <c r="G16" s="36">
         <v>3420</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1205,23 +1199,23 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="28">
         <v>46120</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <v>415545</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="34">
         <v>355503.75</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <v>1003.75</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="37">
+      <c r="F17" s="33"/>
+      <c r="G17" s="36">
         <v>2592</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1238,21 +1232,21 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="28">
         <v>46121</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="34">
         <v>426678</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="34">
         <v>366426</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35">
+      <c r="E18" s="33"/>
+      <c r="F18" s="34">
         <v>1251</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="34"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1269,21 +1263,21 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="28">
         <v>46122</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <v>291054.08000000002</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <v>245777.33</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35">
+      <c r="E19" s="33"/>
+      <c r="F19" s="34">
         <v>104.67</v>
       </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="34"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1300,17 +1294,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="28">
         <v>46123</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1327,17 +1321,17 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1354,24 +1348,24 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="28">
         <v>46125</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="34">
         <v>240718</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="34">
         <v>188040.89</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="33">
         <v>110.39</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37">
+      <c r="F22" s="36"/>
+      <c r="G22" s="36">
         <f>1296</f>
         <v>1296</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="36">
         <v>174.11</v>
       </c>
       <c r="I22" s="1"/>
@@ -1390,23 +1384,23 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="28">
         <v>46126</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="34">
         <v>270579</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="34">
         <v>231296.25</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="37">
+      <c r="E23" s="33"/>
+      <c r="F23" s="36">
         <v>678.75</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="36">
         <v>60</v>
       </c>
-      <c r="H23" s="37"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -1423,23 +1417,23 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="28">
         <v>46127</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="34">
         <v>376385</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="34">
         <v>274893</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="33">
         <v>1406</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37">
+      <c r="F24" s="36"/>
+      <c r="G24" s="36">
         <v>1476</v>
       </c>
-      <c r="H24" s="37"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -1456,21 +1450,21 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="28">
         <v>46128</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="34">
         <v>288771</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="34">
         <v>314444.5</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="37">
+      <c r="E25" s="33"/>
+      <c r="F25" s="36">
         <v>828.5</v>
       </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37">
+      <c r="G25" s="36"/>
+      <c r="H25" s="36">
         <v>40</v>
       </c>
       <c r="I25" s="1"/>
@@ -1489,17 +1483,17 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="28">
         <v>46129</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="45"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="19"/>
@@ -1516,17 +1510,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="28">
         <v>46130</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -1543,17 +1537,17 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -1570,23 +1564,23 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <v>46132</v>
       </c>
       <c r="C29" s="12">
         <v>547809</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>443992.5</v>
       </c>
       <c r="E29" s="15">
         <v>162.5</v>
       </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="36">
+      <c r="G29" s="35">
         <v>3312</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="31"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -1603,23 +1597,23 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="28">
         <v>46133</v>
       </c>
       <c r="C30" s="12">
         <v>439067</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="39">
         <v>380276.75</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="12">
         <v>580.25</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="35">
         <v>2622</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -1636,21 +1630,21 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="28">
         <v>46134</v>
       </c>
       <c r="C31" s="12">
         <v>240726</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="39">
         <v>206967</v>
       </c>
       <c r="E31" s="15">
         <v>434</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="32"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="31"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="19"/>
@@ -1667,21 +1661,21 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>46135</v>
       </c>
       <c r="C32" s="12">
         <v>366981</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="39">
         <v>250535.25</v>
       </c>
       <c r="E32" s="15">
         <v>394.25</v>
       </c>
       <c r="F32" s="12"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="32"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -1698,17 +1692,17 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="28">
         <v>46136</v>
       </c>
-      <c r="C33" s="43" t="s">
+      <c r="C33" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="32">
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="31">
         <v>71260</v>
       </c>
       <c r="I33" s="1"/>
@@ -1727,17 +1721,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="28">
         <v>46137</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -1754,17 +1748,17 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="43"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -1781,7 +1775,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="28">
         <v>46139</v>
       </c>
       <c r="C36" s="12">
@@ -1794,10 +1788,10 @@
       <c r="F36" s="12">
         <v>9.25</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="35">
         <v>3888</v>
       </c>
-      <c r="H36" s="33"/>
+      <c r="H36" s="32"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -1814,7 +1808,7 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="28">
         <v>46140</v>
       </c>
       <c r="C37" s="12">
@@ -1827,10 +1821,10 @@
       <c r="F37" s="12">
         <v>69.61</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <v>2742</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="31">
         <v>92.86</v>
       </c>
       <c r="I37" s="1"/>
@@ -1849,15 +1843,21 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="28">
         <v>46141</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="15"/>
+      <c r="C38" s="12">
+        <v>312197</v>
+      </c>
+      <c r="D38" s="12">
+        <v>258302</v>
+      </c>
+      <c r="E38" s="15">
+        <v>87</v>
+      </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="32"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="31"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -1874,15 +1874,15 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="41"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
       <c r="E39" s="15"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="32"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="31"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -1899,9 +1899,9 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="29"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="40"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -1922,12 +1922,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -1945,7 +1945,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="29"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
@@ -1965,18 +1965,18 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="29"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7183448.0800000001</v>
+        <v>7495645.0800000001</v>
       </c>
       <c r="D43" s="18"/>
-      <c r="E43" s="30">
+      <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4624.1399999999994</v>
+        <v>4711.1399999999994</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="44" spans="1:19" ht="15">
       <c r="A44" s="1"/>
-      <c r="B44" s="31"/>
+      <c r="B44" s="30"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
-      <c r="E44" s="27"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>
@@ -5651,7 +5651,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -5682,23 +5682,23 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="28">
         <v>46113</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>356469</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <v>304701</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35">
+      <c r="E10" s="33"/>
+      <c r="F10" s="34">
         <v>260</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="34">
         <v>1356</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -5715,23 +5715,23 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="28">
         <v>46114</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>278180</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>234894.5</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="33">
         <v>1086.5</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35">
+      <c r="F11" s="33"/>
+      <c r="G11" s="34">
         <v>1944</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -5748,17 +5748,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <v>46115</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -5775,17 +5775,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="28">
         <v>46116</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -5802,17 +5802,17 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -5829,23 +5829,23 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="28">
         <v>46118</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <v>488743</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="34">
         <v>413351.5</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="37">
+      <c r="E15" s="33"/>
+      <c r="F15" s="36">
         <v>2101.5</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="36">
         <v>3006</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -5862,23 +5862,23 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <v>46119</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="34">
         <v>321418</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <v>274279</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="33">
         <v>321</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="37">
+      <c r="F16" s="33"/>
+      <c r="G16" s="36">
         <v>1200</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -5895,23 +5895,23 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="28">
         <v>46120</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <v>286224</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="34">
         <v>286224</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <v>583.75</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="37">
+      <c r="F17" s="33"/>
+      <c r="G17" s="36">
         <v>1494</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -5928,23 +5928,23 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="28">
         <v>46121</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="34">
         <v>256965</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="34">
         <v>217815</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="33">
         <v>187</v>
       </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="37">
+      <c r="F18" s="33"/>
+      <c r="G18" s="36">
         <v>1296</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -5961,23 +5961,23 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="28">
         <v>46122</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <v>337013</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <v>300227.75</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35">
+      <c r="E19" s="33"/>
+      <c r="F19" s="34">
         <v>112.25</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="36">
         <v>1200</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -5994,17 +5994,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="28">
         <v>46123</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -6021,17 +6021,17 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -6048,23 +6048,23 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="28">
         <v>46125</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="34">
         <v>304172</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="34">
         <v>257400.5</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="33">
         <v>1453.5</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37">
+      <c r="F22" s="36"/>
+      <c r="G22" s="36">
         <v>1944</v>
       </c>
-      <c r="H22" s="37"/>
+      <c r="H22" s="36"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -6081,23 +6081,23 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="28">
         <v>46126</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="34">
         <v>326754</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="34">
         <v>273274.5</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="33">
         <v>206.5</v>
       </c>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37">
+      <c r="F23" s="36"/>
+      <c r="G23" s="36">
         <v>2286</v>
       </c>
-      <c r="H23" s="37"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -6114,23 +6114,23 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="28">
         <v>46127</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="34">
         <v>295167</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="34">
         <v>245640</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="37">
+      <c r="E24" s="33"/>
+      <c r="F24" s="36">
         <v>329</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="36">
         <v>2010</v>
       </c>
-      <c r="H24" s="37"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="7"/>
@@ -6147,23 +6147,23 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="28">
         <v>46128</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="34">
         <v>292871</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="34">
         <v>246705.5</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="37">
+      <c r="E25" s="33"/>
+      <c r="F25" s="36">
         <v>524.5</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="36">
         <v>1536</v>
       </c>
-      <c r="H25" s="37"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -6180,23 +6180,23 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="28">
         <v>46129</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="34">
         <v>274543</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="34">
         <v>235897</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="33">
         <v>38</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37">
+      <c r="F26" s="36"/>
+      <c r="G26" s="36">
         <v>1200</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="19"/>
@@ -6213,17 +6213,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="28">
         <v>46130</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -6240,17 +6240,17 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -6267,21 +6267,21 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <v>46132</v>
       </c>
       <c r="C29" s="12">
         <v>387918</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>329710.5</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="12">
         <v>54.5</v>
       </c>
-      <c r="G29" s="36"/>
-      <c r="H29" s="32"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="31"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="7"/>
@@ -6298,23 +6298,23 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="28">
         <v>46133</v>
       </c>
       <c r="C30" s="12">
         <v>302792</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="39">
         <v>254528</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="12">
         <v>613</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="35">
         <v>1332</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -6331,23 +6331,23 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="28">
         <v>46134</v>
       </c>
       <c r="C31" s="12">
         <v>262492</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="39">
         <v>222119.5</v>
       </c>
       <c r="E31" s="15">
         <v>152.5</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="36">
+      <c r="G31" s="35">
         <v>1944</v>
       </c>
-      <c r="H31" s="32"/>
+      <c r="H31" s="31"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="19"/>
@@ -6364,23 +6364,23 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>46135</v>
       </c>
       <c r="C32" s="12">
         <v>289540</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="39">
         <v>238440.25</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="12">
         <v>136.75</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="35">
         <v>2130</v>
       </c>
-      <c r="H32" s="32"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="7"/>
@@ -6397,23 +6397,23 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="28">
         <v>46136</v>
       </c>
       <c r="C33" s="12">
         <v>233535</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="39">
         <v>197946.75</v>
       </c>
       <c r="E33" s="15">
         <v>8.75</v>
       </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="36">
+      <c r="G33" s="35">
         <v>648</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="31"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="7"/>
@@ -6430,17 +6430,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="28">
         <v>46137</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -6457,17 +6457,17 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="43"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -6484,17 +6484,17 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="28">
         <v>46139</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="45"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="7"/>
@@ -6511,7 +6511,7 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="28">
         <v>46140</v>
       </c>
       <c r="C37" s="12">
@@ -6544,15 +6544,23 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="28">
         <v>46141</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="15"/>
+      <c r="C38" s="12">
+        <v>867089</v>
+      </c>
+      <c r="D38" s="12">
+        <v>735448.25</v>
+      </c>
+      <c r="E38" s="13">
+        <v>748.25</v>
+      </c>
       <c r="F38" s="12"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="32"/>
+      <c r="G38" s="12">
+        <v>5970</v>
+      </c>
+      <c r="H38" s="12"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -6569,15 +6577,15 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="15"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="32"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -6594,9 +6602,9 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="29"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="40"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -6617,12 +6625,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -6640,7 +6648,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="29"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
@@ -6660,18 +6668,18 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="29"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5956556</v>
+        <v>6823645</v>
       </c>
       <c r="D43" s="18"/>
-      <c r="E43" s="30">
+      <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4037.5</v>
+        <v>4785.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -6679,7 +6687,7 @@
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>31212</v>
+        <v>37182</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
@@ -6702,7 +6710,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
-      <c r="E44" s="27"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>
@@ -10143,16 +10151,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C34:H34"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10345,7 +10353,7 @@
       <c r="C9" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -10376,23 +10384,23 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="28">
         <v>46113</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>419925</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <v>350714.25</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>211.75</v>
       </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35">
+      <c r="F10" s="33"/>
+      <c r="G10" s="34">
         <v>2226</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -10409,23 +10417,23 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="28">
         <v>46114</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>589177</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>497992.75</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="33">
         <v>144.75</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35">
+      <c r="F11" s="33"/>
+      <c r="G11" s="34">
         <v>3864</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -10442,17 +10450,17 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <v>46115</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -10469,17 +10477,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="28">
         <v>46116</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -10496,17 +10504,17 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -10523,23 +10531,23 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="28">
         <v>46118</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <v>513840</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="34">
         <v>432927.25</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="33">
         <v>490.75</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="37">
+      <c r="F15" s="33"/>
+      <c r="G15" s="36">
         <v>1866</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="36">
         <v>50</v>
       </c>
       <c r="I15" s="1"/>
@@ -10558,23 +10566,23 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <v>46119</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="34">
         <v>709846</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <v>599689</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35">
+      <c r="E16" s="33"/>
+      <c r="F16" s="34">
         <v>320</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="36">
         <v>4944</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -10591,23 +10599,23 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="28">
         <v>46120</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <v>546916</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="34">
         <v>461549</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <v>854</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="37">
+      <c r="F17" s="33"/>
+      <c r="G17" s="36">
         <v>4044</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="34">
         <v>50</v>
       </c>
       <c r="I17" s="1"/>
@@ -10626,23 +10634,23 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="28">
         <v>46121</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="34">
         <v>448958</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="34">
         <v>366583.25</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35">
+      <c r="E18" s="33"/>
+      <c r="F18" s="34">
         <v>1663.75</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="36">
         <v>1296</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -10659,17 +10667,17 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="28">
         <v>46122</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="45"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -10686,17 +10694,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="28">
         <v>46123</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -10713,17 +10721,17 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -10740,23 +10748,23 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="28">
         <v>46125</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="34">
         <v>328634</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="34">
         <v>278277.75</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="33">
         <v>427.75</v>
       </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37">
+      <c r="F22" s="36"/>
+      <c r="G22" s="36">
         <v>1920</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="36">
         <v>50</v>
       </c>
       <c r="I22" s="1"/>
@@ -10775,23 +10783,23 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="28">
         <v>46126</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="34">
         <v>447818</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="34">
         <v>384131</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="37">
+      <c r="E23" s="33"/>
+      <c r="F23" s="36">
         <v>561</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="36">
         <v>2856</v>
       </c>
-      <c r="H23" s="37"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="7"/>
@@ -10808,24 +10816,24 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="28">
         <v>46127</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="34">
         <v>547376</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="34">
         <v>477853</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="33">
         <v>300.5</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37">
+      <c r="F24" s="36"/>
+      <c r="G24" s="36">
         <f>2064</f>
         <v>2064</v>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="36">
         <v>50</v>
       </c>
       <c r="I24" s="1"/>
@@ -10844,23 +10852,23 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="28">
         <v>46128</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="34">
         <v>402605</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="34">
         <v>339884</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="37">
+      <c r="E25" s="33"/>
+      <c r="F25" s="36">
         <v>380</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="36">
         <v>2496</v>
       </c>
-      <c r="H25" s="37"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="7"/>
@@ -10877,23 +10885,23 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="28">
         <v>46129</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="34">
         <v>442271</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="34">
         <v>375419</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="37">
+      <c r="E26" s="33"/>
+      <c r="F26" s="36">
         <v>11107</v>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="36">
         <v>2928</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="19"/>
@@ -10910,17 +10918,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="28">
         <v>46130</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="7"/>
@@ -10937,17 +10945,17 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="43"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="7"/>
@@ -10964,23 +10972,23 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <v>46132</v>
       </c>
       <c r="C29" s="12">
         <v>394839</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>394839</v>
       </c>
       <c r="E29" s="15">
         <v>10236.5</v>
       </c>
       <c r="F29" s="12"/>
-      <c r="G29" s="36">
+      <c r="G29" s="35">
         <v>1956</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="31">
         <v>50</v>
       </c>
       <c r="I29" s="1"/>
@@ -10999,23 +11007,23 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="28">
         <v>46133</v>
       </c>
       <c r="C30" s="12">
         <v>454803</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="39">
         <v>390153.75</v>
       </c>
       <c r="E30" s="15">
         <v>15223.75</v>
       </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="36">
+      <c r="G30" s="35">
         <v>3156</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="7"/>
@@ -11032,23 +11040,23 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="28">
         <v>46134</v>
       </c>
       <c r="C31" s="12">
         <v>359940</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="39">
         <v>306970</v>
       </c>
       <c r="E31" s="15">
         <v>806</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="36">
+      <c r="G31" s="35">
         <v>1758</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="31">
         <v>50</v>
       </c>
       <c r="I31" s="1"/>
@@ -11067,23 +11075,23 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>46135</v>
       </c>
       <c r="C32" s="12">
         <v>315337</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="39">
         <v>254584</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="12">
         <v>1337</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="35">
         <v>648</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="31">
         <v>26145</v>
       </c>
       <c r="I32" s="1"/>
@@ -11102,23 +11110,23 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="28">
         <v>46136</v>
       </c>
       <c r="C33" s="12">
         <v>299078</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="39">
         <v>254793</v>
       </c>
       <c r="E33" s="15">
         <v>1617</v>
       </c>
       <c r="F33" s="12"/>
-      <c r="G33" s="36">
+      <c r="G33" s="35">
         <v>906</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="31">
         <v>50</v>
       </c>
       <c r="I33" s="1"/>
@@ -11137,17 +11145,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="28">
         <v>46137</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="7"/>
@@ -11164,17 +11172,17 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="43"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="7"/>
@@ -11191,7 +11199,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="28">
         <v>46139</v>
       </c>
       <c r="C36" s="12">
@@ -11204,10 +11212,10 @@
       <c r="F36" s="12">
         <v>1591</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="35">
         <v>3036</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="40">
         <v>50</v>
       </c>
       <c r="I36" s="1"/>
@@ -11226,7 +11234,7 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="28">
         <v>46140</v>
       </c>
       <c r="C37" s="12">
@@ -11239,10 +11247,10 @@
       <c r="F37" s="12">
         <v>154.75</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <v>3480</v>
       </c>
-      <c r="H37" s="42"/>
+      <c r="H37" s="40"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="8"/>
@@ -11259,15 +11267,25 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="28">
         <v>46141</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="32"/>
+      <c r="C38" s="12">
+        <v>424964</v>
+      </c>
+      <c r="D38" s="12">
+        <v>366647.25</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="12">
+        <v>506.25</v>
+      </c>
+      <c r="G38" s="35">
+        <v>2580</v>
+      </c>
+      <c r="H38" s="40">
+        <v>50</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7"/>
@@ -11284,15 +11302,15 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="15"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="32"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="40"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7"/>
@@ -11309,9 +11327,9 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="29"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="40"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="15"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
@@ -11332,12 +11350,12 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="29"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -11355,7 +11373,7 @@
       <c r="A42" s="23">
         <v>31</v>
       </c>
-      <c r="B42" s="29"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
@@ -11375,30 +11393,30 @@
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19" ht="15">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="29"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>8175984</v>
+        <v>8600948</v>
       </c>
       <c r="D43" s="18"/>
-      <c r="E43" s="30">
+      <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
         <v>30312.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>17114.5</v>
+        <v>17620.75</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
-        <v>45444</v>
+        <v>48024</v>
       </c>
       <c r="H43" s="18">
         <f>SUM(H10:H42)</f>
-        <v>26545</v>
+        <v>26595</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -11417,7 +11435,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
-      <c r="E44" s="27"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="1"/>

--- a/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SHORT OVER ALL ROUTES - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE3056-F818-4800-BE1A-C4BE35EBA5C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A02F8B-CC38-4FF3-BB52-ABEE33547867}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="APRIL, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1877,10 +1877,16 @@
       <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="C39" s="12">
+        <v>357679</v>
+      </c>
+      <c r="D39" s="12">
+        <v>311164.25</v>
+      </c>
       <c r="E39" s="15"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="12">
+        <v>1536.75</v>
+      </c>
       <c r="G39" s="35"/>
       <c r="H39" s="31"/>
       <c r="I39" s="1"/>
@@ -1971,7 +1977,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>7495645.0800000001</v>
+        <v>7853324.0800000001</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="29">
@@ -1980,7 +1986,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>3522.03</v>
+        <v>5058.7800000000007</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
@@ -6580,9 +6586,15 @@
       <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
+      <c r="C39" s="12">
+        <v>296104</v>
+      </c>
+      <c r="D39" s="12">
+        <v>254794.75</v>
+      </c>
+      <c r="E39" s="13">
+        <v>844.75</v>
+      </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
@@ -6674,12 +6686,12 @@
       <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6823645</v>
+        <v>7119749</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="29">
         <f>SUM(E10:E42)</f>
-        <v>4785.75</v>
+        <v>5630.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10151,16 +10163,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C35:H35"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C35:H35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11305,10 +11317,16 @@
       <c r="B39" s="28">
         <v>46142</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="C39" s="12">
+        <v>546833</v>
+      </c>
+      <c r="D39" s="12">
+        <v>483382.25</v>
+      </c>
       <c r="E39" s="13"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="12">
+        <v>12.75</v>
+      </c>
       <c r="G39" s="35"/>
       <c r="H39" s="40"/>
       <c r="I39" s="1"/>
@@ -11399,7 +11417,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>8600948</v>
+        <v>9147781</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="29">
@@ -11408,7 +11426,7 @@
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
-        <v>17620.75</v>
+        <v>17633.5</v>
       </c>
       <c r="G43" s="18">
         <f>SUM(G10:G42)</f>
